--- a/ivans_data_dictionary.xlsx
+++ b/ivans_data_dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vmivsp-my.sharepoint.com/personal/nilesh_poddaturi_valuemomentum_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SujaySunilNagvekar\VM\Agency Finder\agency_finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_D8441531B8FB85F86815D1D8A24FCDFEBA0070CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8715D23-090D-4FA0-B725-31AAAAB5DAB0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA2E969-2B99-4B18-9A5A-03846D47E1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Policy_Download" sheetId="1" r:id="rId1"/>
@@ -768,7 +768,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1130,14 +1130,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1182,7 +1184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1219,7 +1221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1239,7 +1241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1256,7 +1258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1273,7 +1275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1290,7 +1292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1310,7 +1312,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1330,7 +1332,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1364,7 +1366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -1381,7 +1383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1398,7 +1400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1415,7 +1417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -1432,7 +1434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1449,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1466,7 +1468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -1483,7 +1485,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -1500,7 +1502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -1517,7 +1519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -1534,7 +1536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -1551,7 +1553,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>84</v>
       </c>
@@ -1568,7 +1570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>87</v>
       </c>
@@ -1585,7 +1587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -1602,7 +1604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>92</v>
       </c>
@@ -1619,7 +1621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>95</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -1656,7 +1658,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -1673,7 +1675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -1690,7 +1692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -1707,7 +1709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -1732,9 +1734,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1760,7 +1762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1777,7 +1779,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1794,7 +1796,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -1811,7 +1813,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1831,7 +1833,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1848,7 +1850,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>89</v>
       </c>
@@ -1865,7 +1867,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -1882,7 +1884,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -1899,7 +1901,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -1916,7 +1918,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>136</v>
       </c>
@@ -1941,12 +1943,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1972,7 +1974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1991,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2006,7 +2008,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2026,7 +2028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>144</v>
       </c>
@@ -2043,7 +2045,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -2060,7 +2062,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -2077,7 +2079,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>153</v>
       </c>
@@ -2094,7 +2096,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>156</v>
       </c>
@@ -2111,7 +2113,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -2128,7 +2130,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -2145,7 +2147,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>165</v>
       </c>
@@ -2162,7 +2164,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>168</v>
       </c>
@@ -2179,7 +2181,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>171</v>
       </c>
@@ -2196,7 +2198,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>174</v>
       </c>
@@ -2213,7 +2215,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>177</v>
       </c>
@@ -2230,7 +2232,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>180</v>
       </c>
@@ -2255,9 +2257,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2283,7 +2285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2300,7 +2302,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2317,7 +2319,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2334,7 +2336,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>188</v>
       </c>
@@ -2351,7 +2353,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>191</v>
       </c>
@@ -2368,7 +2370,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>194</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -2410,9 +2412,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2438,7 +2440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -2458,7 +2460,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -2478,7 +2480,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -2498,7 +2500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>210</v>
       </c>
@@ -2526,9 +2528,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2554,7 +2556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>213</v>
       </c>
@@ -2574,7 +2576,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>218</v>
       </c>
@@ -2591,7 +2593,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>221</v>
       </c>
@@ -2616,9 +2618,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2644,7 +2646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>224</v>
       </c>
@@ -2664,7 +2666,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>229</v>
       </c>
@@ -2681,7 +2683,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>233</v>
       </c>
@@ -2698,7 +2700,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>236</v>
       </c>
